--- a/files/sdr.xlsx
+++ b/files/sdr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junqing\Documents\GitHub\junqing-zhang.github.io\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020F5A26-48A5-4BF3-9A92-53137F290B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83C0CE6-54BC-4562-8C76-D445BB350E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
   <si>
     <t>SDR</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Duplex</t>
   </si>
   <si>
-    <t>1 MHz - 6 GHz</t>
-  </si>
-  <si>
     <t>20 MHz</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t>Half</t>
   </si>
   <si>
-    <t>22 MHz - 2.2 GHz</t>
-  </si>
-  <si>
     <t>3.2 MHz</t>
   </si>
   <si>
@@ -78,12 +72,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>70 MHz - 6 GHz</t>
-  </si>
-  <si>
-    <t>61.44 MHz</t>
-  </si>
-  <si>
     <t>12 bits</t>
   </si>
   <si>
@@ -114,12 +102,6 @@
     <t>TwinRx</t>
   </si>
   <si>
-    <t>[USRP X310](https://www.ettus.com/all-products/x310-kit/){:target="_blank"}+ [UBX 160 USRP RF Daughterboard](https://www.ettus.com/all-products/ubx160/)</t>
-  </si>
-  <si>
-    <t>[USRP X310](https://www.ettus.com/all-products/x310-kit/){:target="_blank"} + [TwinRX RF Daughterboard](https://www.ettus.com/all-products/twinrx/){:target="_blank"}</t>
-  </si>
-  <si>
     <t xml:space="preserve">[USRP N210](https://www.ettus.com/all-products/un210-kit/){:target="_blank"} + [UBX 40 USRP RF Daughterboard](https://www.ettus.com/all-products/ubx40/){:target="_blank"} </t>
   </si>
   <si>
@@ -151,6 +133,66 @@
   </si>
   <si>
     <t>[RTL-SDR](https://www.rtl-sdr.com/about-rtl-sdr/){:target="_blank"}</t>
+  </si>
+  <si>
+    <t>AD9364</t>
+  </si>
+  <si>
+    <t>AD9363</t>
+  </si>
+  <si>
+    <t>325 MHz to 3.8 GHz</t>
+  </si>
+  <si>
+    <t>47 MHz to 6 GHz</t>
+  </si>
+  <si>
+    <t>1 MHz to 6 GHz</t>
+  </si>
+  <si>
+    <t>22 MHz to 2.2 GHz</t>
+  </si>
+  <si>
+    <t>70 MHz to 6 GHz</t>
+  </si>
+  <si>
+    <t>61.44MHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56 MHz </t>
+  </si>
+  <si>
+    <t>10 MHz to 6 GHz</t>
+  </si>
+  <si>
+    <t>40 MHz</t>
+  </si>
+  <si>
+    <t>80 MHz</t>
+  </si>
+  <si>
+    <t>100 MSPS</t>
+  </si>
+  <si>
+    <t>160 MHz</t>
+  </si>
+  <si>
+    <t>14 bits</t>
+  </si>
+  <si>
+    <t>[USRP X310](https://www.ettus.com/all-products/x310-kit/){:target="_blank"}+ [UBX 160 USRP RF Daughterboard](https://www.ettus.com/all-products/ubx160/)x2</t>
+  </si>
+  <si>
+    <t>[USRP X310](https://www.ettus.com/all-products/x310-kit/){:target="_blank"} + [TwinRX RF Daughterboard](https://www.ettus.com/all-products/twinrx/){:target="_blank"}x2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 MHz to 6 GHz </t>
+  </si>
+  <si>
+    <t>56 MHz</t>
+  </si>
+  <si>
+    <t>Full </t>
   </si>
 </sst>
 </file>
@@ -487,7 +529,7 @@
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="173.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
@@ -524,69 +566,103 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I3" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="I4" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
@@ -595,160 +671,246 @@
         <v>2</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>25</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/files/sdr.xlsx
+++ b/files/sdr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junqing\Documents\GitHub\junqing-zhang.github.io\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83C0CE6-54BC-4562-8C76-D445BB350E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279D8E4C-6FD0-4078-82F6-B0956B3B9C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
   <si>
     <t>SDR</t>
   </si>
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="173.88671875" bestFit="1" customWidth="1"/>
@@ -736,62 +736,54 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>15</v>
@@ -814,103 +806,151 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
